--- a/data/ENPRA (TRY).xlsx
+++ b/data/ENPRA (TRY).xlsx
@@ -4,12 +4,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Bilanço" sheetId="1" r:id="rId1"/>
-    <sheet name="Gelir Tablosu (Dönemsel)" sheetId="2" r:id="rId2"/>
-    <sheet name="Gelir Tablosu (Çeyreklik)" sheetId="3" r:id="rId3"/>
-    <sheet name="Gelir Tablosu (Yıllıklan.)" sheetId="4" r:id="rId4"/>
-    <sheet name="Nakit Akış (Dönemsel)" sheetId="5" r:id="rId5"/>
-    <sheet name="Nakit Akış (Çeyreklik)" sheetId="6" r:id="rId6"/>
-    <sheet name="Nakit Akış (Yıllıklan.)" sheetId="7" r:id="rId7"/>
+    <sheet name="Gelir tablosu (dönemsel)" sheetId="2" r:id="rId2"/>
+    <sheet name="Gelir tablosu (çeyreklik)" sheetId="3" r:id="rId3"/>
+    <sheet name="Gelir tablosu (yıllıklan.)" sheetId="4" r:id="rId4"/>
+    <sheet name="Nakit akış (dönemsel)" sheetId="5" r:id="rId5"/>
+    <sheet name="Nakit akış (çeyreklik)" sheetId="6" r:id="rId6"/>
+    <sheet name="Nakit akış (yıllıklan.)" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -37,28 +37,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="none">
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -67,13 +77,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -403,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:G57"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -411,1083 +423,1240 @@
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="2" t="str">
         <v>Kalem</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" s="2" t="str">
+        <v>2026/9</v>
+      </c>
+      <c r="C1" s="2" t="str">
         <v>2026/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" s="2" t="str">
         <v>2026/3</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" s="2" t="str">
         <v>2025/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" s="2" t="str">
         <v>2025/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" s="2" t="str">
         <v>2024/12</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" s="2" t="str">
         <v>Finansal Varlıklar (Net)</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3" s="2" t="str">
         <v xml:space="preserve">    FİNANSAL VARLIKLAR (Net)</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
+        <v>109468000000</v>
+      </c>
+      <c r="C3" s="2">
         <v>108359000000</v>
       </c>
-      <c r="C3">
+      <c r="D3" s="2">
         <v>106668720000</v>
       </c>
-      <c r="D3">
+      <c r="E3" s="2">
         <v>91883000000</v>
       </c>
-      <c r="E3">
+      <c r="F3" s="2">
         <v>73395086000</v>
       </c>
-      <c r="F3">
+      <c r="G3" s="2">
         <v>7923749000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4" s="2" t="str">
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
+        <v>85816000000</v>
+      </c>
+      <c r="C4" s="2">
         <v>84204000000</v>
       </c>
-      <c r="C4">
+      <c r="D4" s="2">
         <v>87645307000</v>
       </c>
-      <c r="D4">
+      <c r="E4" s="2">
         <v>76811000000</v>
       </c>
-      <c r="E4">
+      <c r="F4" s="2">
         <v>61014972000</v>
       </c>
-      <c r="F4">
+      <c r="G4" s="2">
         <v>7923749000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5" s="2" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Farkı Kâr Zarara Yansıtılan Finansal Varlıklar</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
+      <c r="B5" s="2">
+        <v>95000000</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6" s="2" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Farkı Diğer Kapsamlı Gelire Yansıtılan Finansal Varlıklar</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
+        <v>23284000000</v>
+      </c>
+      <c r="C6" s="2">
         <v>24154000000</v>
       </c>
-      <c r="C6">
+      <c r="D6" s="2">
         <v>18314843000</v>
       </c>
-      <c r="D6">
+      <c r="E6" s="2">
         <v>13937000000</v>
       </c>
-      <c r="E6">
+      <c r="F6" s="2">
         <v>11984636000</v>
       </c>
-      <c r="F6">
+      <c r="G6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
+      <c r="A7" s="2" t="str">
         <v xml:space="preserve">    İtfa Edilmiş Maliyeti ile Ölçülen Finansal Varlıklar</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
+        <v>18407000000</v>
+      </c>
+      <c r="C7" s="2">
         <v>16158000000</v>
       </c>
-      <c r="C7">
+      <c r="D7" s="2">
         <v>15493111000</v>
       </c>
-      <c r="D7">
+      <c r="E7" s="2">
         <v>8612000000</v>
       </c>
-      <c r="E7">
+      <c r="F7" s="2">
         <v>8337286000</v>
       </c>
-      <c r="F7">
+      <c r="G7" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
+      <c r="A8" s="2" t="str">
         <v xml:space="preserve">    Türev Finansal Varlıklar</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
+        <v>273000000</v>
+      </c>
+      <c r="C8" s="2">
         <v>1000000</v>
       </c>
-      <c r="C8">
+      <c r="D8" s="2">
         <v>708570000</v>
       </c>
-      <c r="D8">
+      <c r="E8" s="2">
         <v>1135000000</v>
       </c>
-      <c r="E8">
+      <c r="F8" s="2">
         <v>395478000</v>
       </c>
-      <c r="F8">
+      <c r="G8" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9" s="2" t="str">
         <v xml:space="preserve">    Donuk Finansal Varlıklar</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
+      <c r="A10" s="2" t="str">
         <v xml:space="preserve">    Beklenen Zarar Karşılıkları (-)</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
+      <c r="A11" s="2" t="str">
         <v xml:space="preserve">    KREDİLER (Net)</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
+        <v>193590000000</v>
+      </c>
+      <c r="C11" s="2">
         <v>181654000000</v>
       </c>
-      <c r="C11">
+      <c r="D11" s="2">
         <v>167641703000</v>
       </c>
-      <c r="D11">
+      <c r="E11" s="2">
         <v>152901000000</v>
       </c>
-      <c r="E11">
+      <c r="F11" s="2">
         <v>141428640000</v>
       </c>
-      <c r="F11">
+      <c r="G11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
+      <c r="A12" s="2" t="str">
         <v xml:space="preserve">    Krediler</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
+        <v>187904000000</v>
+      </c>
+      <c r="C12" s="2">
         <v>176529000000</v>
       </c>
-      <c r="C12">
+      <c r="D12" s="2">
         <v>163812310000</v>
       </c>
-      <c r="D12">
+      <c r="E12" s="2">
         <v>154736000000</v>
       </c>
-      <c r="E12">
+      <c r="F12" s="2">
         <v>141939867000</v>
       </c>
-      <c r="F12">
+      <c r="G12" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
+      <c r="A13" s="2" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Alacaklar</v>
       </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
+      <c r="A14" s="2" t="str">
         <v xml:space="preserve">    Faktoring Alacakları</v>
       </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
+      <c r="A15" s="2" t="str">
         <v xml:space="preserve">    Donuk Alacaklar</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
+      <c r="A16" s="2" t="str">
         <v xml:space="preserve">    Beklenen Zarar Karşılıkları (-)</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
+        <v>-12721000000</v>
+      </c>
+      <c r="C16" s="2">
         <v>-11033000000</v>
       </c>
-      <c r="C16">
+      <c r="D16" s="2">
         <v>-11663718000</v>
       </c>
-      <c r="D16">
+      <c r="E16" s="2">
         <v>-10447000000</v>
       </c>
-      <c r="E16">
+      <c r="F16" s="2">
         <v>-8848513000</v>
       </c>
-      <c r="F16">
+      <c r="G16" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
+      <c r="A17" s="2" t="str">
         <v xml:space="preserve">    SATIŞ AMAÇLI ELDE TUTULAN VE DURDURULAN FAALİYETLERE İLİŞKİN DURAN VARLIKLAR (Net)</v>
       </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
+      <c r="A18" s="2" t="str">
         <v xml:space="preserve">    ORTAKLIK YATIRIMLARI</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
+      <c r="A19" s="2" t="str">
         <v xml:space="preserve">    İştirakler (Net)</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
+      <c r="A20" s="2" t="str">
         <v xml:space="preserve">    Bağlı Ortaklıklar (Net)</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
+      <c r="A21" s="2" t="str">
         <v xml:space="preserve">    Birlikte Kontrol Edilen Ortaklıklar (İş Ortaklıkları) (Net)</v>
       </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
+      <c r="A22" s="2" t="str">
         <v xml:space="preserve">    MADDİ DURAN VARLIKLAR (Net)</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
+        <v>1498000000</v>
+      </c>
+      <c r="C22" s="2">
         <v>1502000000</v>
       </c>
-      <c r="C22">
+      <c r="D22" s="2">
         <v>1620484000</v>
       </c>
-      <c r="D22">
+      <c r="E22" s="2">
         <v>1721000000</v>
       </c>
-      <c r="E22">
+      <c r="F22" s="2">
         <v>1372636000</v>
       </c>
-      <c r="F22">
+      <c r="G22" s="2">
         <v>1429055000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
+      <c r="A23" s="2" t="str">
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar (Net)</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
+        <v>1676000000</v>
+      </c>
+      <c r="C23" s="2">
         <v>1465000000</v>
       </c>
-      <c r="C23">
+      <c r="D23" s="2">
         <v>1234778000</v>
       </c>
-      <c r="D23">
+      <c r="E23" s="2">
         <v>988000000</v>
       </c>
-      <c r="E23">
+      <c r="F23" s="2">
         <v>783606000</v>
       </c>
-      <c r="F23">
+      <c r="G23" s="2">
         <v>107159000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
+      <c r="A24" s="2" t="str">
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller (Net)</v>
       </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
+      <c r="A25" s="2" t="str">
         <v xml:space="preserve">    Cari Vergi Varlığı</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
+      <c r="B25" s="2">
+        <v>150000000</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
         <v>23000000</v>
       </c>
-      <c r="E25">
+      <c r="F25" s="2">
         <v>323309000</v>
       </c>
-      <c r="F25">
+      <c r="G25" s="2">
         <v>2574000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
+      <c r="A26" s="2" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
+        <v>551000000</v>
+      </c>
+      <c r="C26" s="2">
         <v>1697000000</v>
       </c>
-      <c r="C26">
+      <c r="D26" s="2">
         <v>1183307000</v>
       </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
         <v>330281000</v>
       </c>
-      <c r="F26">
+      <c r="G26" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
+      <c r="A27" s="2" t="str">
         <v xml:space="preserve">    Diğer Aktifler</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
+        <v>4586000000</v>
+      </c>
+      <c r="C27" s="2">
         <v>7114000000</v>
       </c>
-      <c r="C27">
+      <c r="D27" s="2">
         <v>5999077000</v>
       </c>
-      <c r="D27">
+      <c r="E27" s="2">
         <v>2632000000</v>
       </c>
-      <c r="E27">
+      <c r="F27" s="2">
         <v>2764809000</v>
       </c>
-      <c r="F27">
+      <c r="G27" s="2">
         <v>231676000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
+      <c r="A28" s="2" t="str">
         <v xml:space="preserve">    VARLIKLAR TOPLAMI</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
+        <v>311519000000</v>
+      </c>
+      <c r="C28" s="2">
         <v>301791000000</v>
       </c>
-      <c r="C28">
+      <c r="D28" s="2">
         <v>284348069000</v>
       </c>
-      <c r="D28">
+      <c r="E28" s="2">
         <v>250148000000</v>
       </c>
-      <c r="E28">
+      <c r="F28" s="2">
         <v>220398367000</v>
       </c>
-      <c r="F28">
+      <c r="G28" s="2">
         <v>9694213000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
+      <c r="A29" s="2" t="str">
         <v xml:space="preserve">    Mevduat</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
+        <v>240625000000</v>
+      </c>
+      <c r="C29" s="2">
         <v>231921000000</v>
       </c>
-      <c r="C29">
+      <c r="D29" s="2">
         <v>223762771000</v>
       </c>
-      <c r="D29">
+      <c r="E29" s="2">
         <v>205483000000</v>
       </c>
-      <c r="E29">
+      <c r="F29" s="2">
         <v>196815464000</v>
       </c>
-      <c r="F29">
+      <c r="G29" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
+      <c r="A30" s="2" t="str">
         <v xml:space="preserve">    Toplanan Fonlar</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
+      <c r="A31" s="2" t="str">
         <v xml:space="preserve">    Alınan Krediler</v>
       </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
+      <c r="A32" s="2" t="str">
         <v xml:space="preserve">    Para Piyasasına Borçlar</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="2">
+        <v>25077000000</v>
+      </c>
+      <c r="C32" s="2">
         <v>25028000000</v>
       </c>
-      <c r="C32">
+      <c r="D32" s="2">
         <v>20021918000</v>
       </c>
-      <c r="D32">
+      <c r="E32" s="2">
         <v>9888000000</v>
       </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
+      <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
+      <c r="A33" s="2" t="str">
         <v xml:space="preserve">    İhraç Edilen Menkul Kıymetler (Net)</v>
       </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
+      <c r="A34" s="2" t="str">
         <v xml:space="preserve">    Bonolar</v>
       </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
+      <c r="A35" s="2" t="str">
         <v xml:space="preserve">    Varlığa Dayalı Menkul Kıymetler</v>
       </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
+      <c r="A36" s="2" t="str">
         <v xml:space="preserve">    Tahviller</v>
       </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
+      <c r="A37" s="2" t="str">
         <v xml:space="preserve">    Fonlar</v>
       </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
+      <c r="A38" s="2" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Farkı Kar Zarara Yansıtılan Finansal Yükümlülükler</v>
       </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
+      <c r="A39" s="2" t="str">
         <v xml:space="preserve">    Türev Finansal Yükümlülükler</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="2">
+        <v>1237000000</v>
+      </c>
+      <c r="C39" s="2">
         <v>4364000000</v>
       </c>
-      <c r="C39">
+      <c r="D39" s="2">
         <v>3758629000</v>
       </c>
-      <c r="D39">
+      <c r="E39" s="2">
         <v>435000000</v>
       </c>
-      <c r="E39">
+      <c r="F39" s="2">
         <v>39000</v>
       </c>
-      <c r="F39">
+      <c r="G39" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
+      <c r="A40" s="2" t="str">
         <v xml:space="preserve">    Faktoring Yükümlülükleri</v>
       </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
+      <c r="B40" s="2">
+        <v>0</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
+      <c r="A41" s="2" t="str">
         <v xml:space="preserve">    Kiralama İşlemlerinden Yükümlülükler</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="2">
+        <v>250000000</v>
+      </c>
+      <c r="C41" s="2">
         <v>272000000</v>
       </c>
-      <c r="C41">
+      <c r="D41" s="2">
         <v>253822000</v>
       </c>
-      <c r="D41">
+      <c r="E41" s="2">
         <v>245000000</v>
       </c>
-      <c r="E41">
+      <c r="F41" s="2">
         <v>60419000</v>
       </c>
-      <c r="F41">
+      <c r="G41" s="2">
         <v>3114000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
+      <c r="A42" s="2" t="str">
         <v xml:space="preserve">    Karşılıklar</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="2">
+        <v>1182000000</v>
+      </c>
+      <c r="C42" s="2">
         <v>701000000</v>
       </c>
-      <c r="C42">
+      <c r="D42" s="2">
         <v>588824000</v>
       </c>
-      <c r="D42">
+      <c r="E42" s="2">
         <v>622000000</v>
       </c>
-      <c r="E42">
+      <c r="F42" s="2">
         <v>526967000</v>
       </c>
-      <c r="F42">
+      <c r="G42" s="2">
         <v>13799000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
+      <c r="A43" s="2" t="str">
         <v xml:space="preserve">    Cari Vergi Borcu</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="2">
+        <v>0</v>
+      </c>
+      <c r="C43" s="2">
         <v>1233000000</v>
       </c>
-      <c r="C43">
+      <c r="D43" s="2">
         <v>1981023000</v>
       </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
+      <c r="A44" s="2" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Borcu</v>
       </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
+      <c r="B44" s="2">
+        <v>0</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2">
         <v>184000000</v>
       </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
+      <c r="F44" s="2">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2">
         <v>37759000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
+      <c r="A45" s="2" t="str">
         <v xml:space="preserve">    Satış Amaçlı Elde Tutulan Ve Durdurulan Faaliyetlere İlişkin Duran Varlık Borçları (Net)</v>
       </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
+      <c r="B45" s="2">
+        <v>0</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0</v>
+      </c>
+      <c r="G45" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
+      <c r="A46" s="2" t="str">
         <v xml:space="preserve">    Sermaye Benzeri Borçlanma Araçları</v>
       </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
+      <c r="B46" s="2">
+        <v>0</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
+      <c r="A47" s="2" t="str">
         <v xml:space="preserve">    Diğer Yükümlülükler</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="2">
+        <v>18039000000</v>
+      </c>
+      <c r="C47" s="2">
         <v>15647000000</v>
       </c>
-      <c r="C47">
+      <c r="D47" s="2">
         <v>13408676000</v>
       </c>
-      <c r="D47">
+      <c r="E47" s="2">
         <v>14381000000</v>
       </c>
-      <c r="E47">
+      <c r="F47" s="2">
         <v>6092250000</v>
       </c>
-      <c r="F47">
+      <c r="G47" s="2">
         <v>439856000</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="str">
+      <c r="A48" s="2" t="str">
         <v xml:space="preserve">    ÖZKAYNAKLAR</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="2">
+        <v>25109000000</v>
+      </c>
+      <c r="C48" s="2">
         <v>22625000000</v>
       </c>
-      <c r="C48">
+      <c r="D48" s="2">
         <v>20572406000</v>
       </c>
-      <c r="D48">
+      <c r="E48" s="2">
         <v>18910000000</v>
       </c>
-      <c r="E48">
+      <c r="F48" s="2">
         <v>16903228000</v>
       </c>
-      <c r="F48">
+      <c r="G48" s="2">
         <v>9199685000</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
+      <c r="A49" s="2" t="str">
         <v xml:space="preserve">    Ödenmiş Sermaye</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="2">
         <v>12475000000</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="2">
+        <v>12475000000</v>
+      </c>
+      <c r="D49" s="2">
         <v>12475290000</v>
       </c>
-      <c r="D49">
+      <c r="E49" s="2">
         <v>12475000000</v>
       </c>
-      <c r="E49">
+      <c r="F49" s="2">
         <v>12475290000</v>
       </c>
-      <c r="F49">
+      <c r="G49" s="2">
         <v>8684430000</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
+      <c r="A50" s="2" t="str">
         <v xml:space="preserve">    Sermaye Yedekleri</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="2">
         <v>290000000</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="2">
+        <v>290000000</v>
+      </c>
+      <c r="D50" s="2">
         <v>290340000</v>
       </c>
-      <c r="D50">
+      <c r="E50" s="2">
         <v>290000000</v>
       </c>
-      <c r="E50">
+      <c r="F50" s="2">
         <v>295283000</v>
       </c>
-      <c r="F50">
+      <c r="G50" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str">
+      <c r="A51" s="2" t="str">
         <v xml:space="preserve">    Kâr veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler veya Giderler</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="2">
         <v>-21000000</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="2">
+        <v>-21000000</v>
+      </c>
+      <c r="D51" s="2">
         <v>-21158000</v>
       </c>
-      <c r="D51">
+      <c r="E51" s="2">
         <v>-21000000</v>
       </c>
-      <c r="E51">
+      <c r="F51" s="2">
         <v>-103000</v>
       </c>
-      <c r="F51">
+      <c r="G51" s="2">
         <v>-103000</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="str">
+      <c r="A52" s="2" t="str">
         <v xml:space="preserve">    Kâr veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler veya Giderler</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="2">
+        <v>-102000000</v>
+      </c>
+      <c r="C52" s="2">
         <v>-158000000</v>
       </c>
-      <c r="C52">
+      <c r="D52" s="2">
         <v>-264461000</v>
       </c>
-      <c r="D52">
+      <c r="E52" s="2">
         <v>-5000000</v>
       </c>
-      <c r="E52">
+      <c r="F52" s="2">
         <v>-310849000</v>
       </c>
-      <c r="F52">
+      <c r="G52" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="str">
+      <c r="A53" s="2" t="str">
         <v xml:space="preserve">    Kar Yedekleri</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="2">
         <v>6171000000</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="2">
+        <v>6171000000</v>
+      </c>
+      <c r="D53" s="2">
         <v>6171295000</v>
       </c>
-      <c r="D53">
+      <c r="E53" s="2">
         <v>33000000</v>
       </c>
-      <c r="E53">
+      <c r="F53" s="2">
         <v>33423000</v>
       </c>
-      <c r="F53">
+      <c r="G53" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="str">
+      <c r="A54" s="2" t="str">
         <v xml:space="preserve">    Kar veya Zarar</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="2">
+        <v>6296000000</v>
+      </c>
+      <c r="C54" s="2">
         <v>3868000000</v>
       </c>
-      <c r="C54">
+      <c r="D54" s="2">
         <v>1921100000</v>
       </c>
-      <c r="D54">
+      <c r="E54" s="2">
         <v>6138000000</v>
       </c>
-      <c r="E54">
+      <c r="F54" s="2">
         <v>4410184000</v>
       </c>
-      <c r="F54">
+      <c r="G54" s="2">
         <v>515358000</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="str">
+      <c r="A55" s="2" t="str">
         <v xml:space="preserve">    Geçmiş Yıllar Kar veya Zararı</v>
       </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
+      <c r="B55" s="2">
+        <v>0</v>
+      </c>
+      <c r="C55" s="2">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2">
         <v>482000000</v>
       </c>
-      <c r="E55">
+      <c r="F55" s="2">
         <v>481935000</v>
       </c>
-      <c r="F55">
+      <c r="G55" s="2">
         <v>-153097000</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="str">
+      <c r="A56" s="2" t="str">
         <v xml:space="preserve">    Dönem Net Kâr veya Zararı</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="2">
+        <v>6296000000</v>
+      </c>
+      <c r="C56" s="2">
         <v>3868000000</v>
       </c>
-      <c r="C56">
+      <c r="D56" s="2">
         <v>1921100000</v>
       </c>
-      <c r="D56">
+      <c r="E56" s="2">
         <v>5656000000</v>
       </c>
-      <c r="E56">
+      <c r="F56" s="2">
         <v>3928249000</v>
       </c>
-      <c r="F56">
+      <c r="G56" s="2">
         <v>668455000</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="str">
+      <c r="A57" s="2" t="str">
         <v xml:space="preserve">    YÜKÜMLÜLÜKLER TOPLAMI</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="2">
+        <v>311519000000</v>
+      </c>
+      <c r="C57" s="2">
         <v>301791000000</v>
       </c>
-      <c r="C57">
+      <c r="D57" s="2">
         <v>284348069000</v>
       </c>
-      <c r="D57">
+      <c r="E57" s="2">
         <v>250148000000</v>
       </c>
-      <c r="E57">
+      <c r="F57" s="2">
         <v>220398367000</v>
       </c>
-      <c r="F57">
+      <c r="G57" s="2">
         <v>9694213000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G57"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:J46"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1498,1256 +1667,1383 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="2" t="str">
         <v>Kalem</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" s="2" t="str">
+        <v>2026/9</v>
+      </c>
+      <c r="C1" s="2" t="str">
         <v>2026/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" s="2" t="str">
         <v>2026/3</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" s="2" t="str">
         <v>2025/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" s="2" t="str">
         <v>2025/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" s="2" t="str">
         <v>2025/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" s="2" t="str">
         <v>2025/3</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" s="2" t="str">
         <v>2024/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" s="2" t="str">
         <v>2024/9</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" s="2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3" s="2" t="str">
         <v xml:space="preserve">    FAİZ GELİRLERİ</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
+        <v>57850000000</v>
+      </c>
+      <c r="C3" s="2">
         <v>36469000000</v>
       </c>
-      <c r="C3">
+      <c r="D3" s="2">
         <v>17036000000</v>
       </c>
-      <c r="D3">
+      <c r="E3" s="2">
         <v>26460324000</v>
       </c>
-      <c r="E3">
-        <v>8957834000</v>
-      </c>
-      <c r="F3">
+      <c r="F3" s="2">
+        <v>8957000000</v>
+      </c>
+      <c r="G3" s="2">
         <v>1746000000</v>
       </c>
-      <c r="G3">
+      <c r="H3" s="2">
         <v>795000000</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="2">
         <v>296810000</v>
       </c>
-      <c r="I3">
+      <c r="J3" s="2">
         <v>200857000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4" s="2" t="str">
         <v xml:space="preserve">    KAR PAYI GELİRİ</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5" s="2" t="str">
         <v xml:space="preserve">    Kredilerden Alınan Faizler</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
+        <v>41491000000</v>
+      </c>
+      <c r="C5" s="2">
         <v>26316000000</v>
       </c>
-      <c r="C5">
+      <c r="D5" s="2">
         <v>12545000000</v>
       </c>
-      <c r="D5">
+      <c r="E5" s="2">
         <v>16749230000</v>
       </c>
-      <c r="E5">
-        <v>4447673000</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
+      <c r="F5" s="2">
+        <v>4448000000</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6" s="2" t="str">
         <v xml:space="preserve">    Zorunlu Karşılıklardan Alınan Faizler</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
+        <v>7508000000</v>
+      </c>
+      <c r="C6" s="2">
         <v>4889000000</v>
       </c>
-      <c r="C6">
+      <c r="D6" s="2">
         <v>2276000000</v>
       </c>
-      <c r="D6">
+      <c r="E6" s="2">
         <v>3022148000</v>
       </c>
-      <c r="E6">
-        <v>882627000</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="F6" s="2">
+        <v>883000000</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
+      <c r="A7" s="2" t="str">
         <v xml:space="preserve">    Bankalardan Alınan Faizler</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
+        <v>794000000</v>
+      </c>
+      <c r="C7" s="2">
         <v>454000000</v>
       </c>
-      <c r="C7">
+      <c r="D7" s="2">
         <v>201000000</v>
       </c>
-      <c r="D7">
+      <c r="E7" s="2">
         <v>2139144000</v>
       </c>
-      <c r="E7">
-        <v>1352344000</v>
-      </c>
-      <c r="F7">
+      <c r="F7" s="2">
+        <v>1352000000</v>
+      </c>
+      <c r="G7" s="2">
         <v>325000000</v>
       </c>
-      <c r="G7">
+      <c r="H7" s="2">
         <v>311000000</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="2">
         <v>181219000</v>
       </c>
-      <c r="I7">
+      <c r="J7" s="2">
         <v>85266000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
+      <c r="A8" s="2" t="str">
         <v xml:space="preserve">    Para Piyasası İşlemlerinden Alınan Faizler</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>8000000</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
+      <c r="C8" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
         <v>2089000000</v>
       </c>
-      <c r="E8">
-        <v>1671159000</v>
-      </c>
-      <c r="F8">
+      <c r="F8" s="2">
+        <v>1671000000</v>
+      </c>
+      <c r="G8" s="2">
         <v>1408000000</v>
       </c>
-      <c r="G8">
+      <c r="H8" s="2">
         <v>483000000</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="2">
         <v>115591000</v>
       </c>
-      <c r="I8">
+      <c r="J8" s="2">
         <v>115591000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9" s="2" t="str">
         <v xml:space="preserve">    Menkul Değerlerden Alınan Faizler</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
+        <v>8044000000</v>
+      </c>
+      <c r="C9" s="2">
         <v>4799000000</v>
       </c>
-      <c r="C9">
+      <c r="D9" s="2">
         <v>2011000000</v>
       </c>
-      <c r="D9">
+      <c r="E9" s="2">
         <v>2460786000</v>
       </c>
-      <c r="E9">
-        <v>604031000</v>
-      </c>
-      <c r="F9">
+      <c r="F9" s="2">
+        <v>603000000</v>
+      </c>
+      <c r="G9" s="2">
         <v>13000000</v>
       </c>
-      <c r="G9">
+      <c r="H9" s="2">
         <v>1000000</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
+      <c r="A10" s="2" t="str">
         <v xml:space="preserve">    Finansal Kiralama Gelirleri</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
+      <c r="A11" s="2" t="str">
         <v xml:space="preserve">    Diğer Faiz Gelirleri</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="C11" s="2">
         <v>3000000</v>
       </c>
-      <c r="C11">
+      <c r="D11" s="2">
         <v>3000000</v>
       </c>
-      <c r="D11">
+      <c r="E11" s="2">
         <v>16000</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
+      <c r="A12" s="2" t="str">
         <v xml:space="preserve">    FAİZ GİDERLERİ (-)</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
+        <v>-39244000000</v>
+      </c>
+      <c r="C12" s="2">
         <v>-25669000000</v>
       </c>
-      <c r="C12">
+      <c r="D12" s="2">
         <v>-11727000000</v>
       </c>
-      <c r="D12">
+      <c r="E12" s="2">
         <v>-16684686000</v>
       </c>
-      <c r="E12">
-        <v>-4627216000</v>
-      </c>
-      <c r="F12">
+      <c r="F12" s="2">
+        <v>-4627000000</v>
+      </c>
+      <c r="G12" s="2">
         <v>-16000000</v>
       </c>
-      <c r="G12">
+      <c r="H12" s="2">
         <v>-6000000</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="2">
         <v>-4134000</v>
       </c>
-      <c r="I12">
+      <c r="J12" s="2">
         <v>-3900000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
+      <c r="A13" s="2" t="str">
         <v xml:space="preserve">    KAR PAYI GİDERLERİ (-)</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
+      <c r="A14" s="2" t="str">
         <v xml:space="preserve">    Mevduata Verilen Faizler</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
+        <v>-38054000000</v>
+      </c>
+      <c r="C14" s="2">
         <v>-24792000000</v>
       </c>
-      <c r="C14">
+      <c r="D14" s="2">
         <v>-11396000000</v>
       </c>
-      <c r="D14">
+      <c r="E14" s="2">
         <v>-16524396000</v>
       </c>
-      <c r="E14">
-        <v>-4608337000</v>
-      </c>
-      <c r="F14">
+      <c r="F14" s="2">
+        <v>-4608000000</v>
+      </c>
+      <c r="G14" s="2">
         <v>-1000000</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
+      <c r="A15" s="2" t="str">
         <v xml:space="preserve">    Kullanılan Kredilere Verilen Faizler</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>-1000000</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>-1000000</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>-562000</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
+      <c r="D15" s="2">
+        <v>-1000000</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>-1000000</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
         <v>-3000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
+      <c r="A16" s="2" t="str">
         <v xml:space="preserve">    Para Piyasası İşlemlerine Verilen Faizler</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
+        <v>-1061000000</v>
+      </c>
+      <c r="C16" s="2">
         <v>-792000000</v>
       </c>
-      <c r="C16">
+      <c r="D16" s="2">
         <v>-293000000</v>
       </c>
-      <c r="D16">
+      <c r="E16" s="2">
         <v>-110082000</v>
       </c>
-      <c r="E16">
-        <v>-4000</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
+      <c r="A17" s="2" t="str">
         <v xml:space="preserve">    İhraç Edilen Menkul Kıymetlere Verilen Faizler</v>
       </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
+      <c r="A18" s="2" t="str">
         <v xml:space="preserve">    Diğer Faiz Giderleri</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
+        <v>-50000000</v>
+      </c>
+      <c r="C18" s="2">
         <v>-30000000</v>
       </c>
-      <c r="C18">
+      <c r="D18" s="2">
         <v>-7000000</v>
       </c>
-      <c r="D18">
+      <c r="E18" s="2">
         <v>-24870000</v>
       </c>
-      <c r="E18">
-        <v>-12859000</v>
-      </c>
-      <c r="F18">
+      <c r="F18" s="2">
+        <v>-13000000</v>
+      </c>
+      <c r="G18" s="2">
         <v>-11000000</v>
       </c>
-      <c r="G18">
+      <c r="H18" s="2">
         <v>-4000000</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="2">
         <v>-3525000</v>
       </c>
-      <c r="I18">
+      <c r="J18" s="2">
         <v>-3525000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
+      <c r="A19" s="2" t="str">
         <v xml:space="preserve">    NET FAİZ GELİRİ VEYA GİDERİ</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
+        <v>18606000000</v>
+      </c>
+      <c r="C19" s="2">
         <v>10800000000</v>
       </c>
-      <c r="C19">
+      <c r="D19" s="2">
         <v>5309000000</v>
       </c>
-      <c r="D19">
+      <c r="E19" s="2">
         <v>9775638000</v>
       </c>
-      <c r="E19">
-        <v>4330618000</v>
-      </c>
-      <c r="F19">
+      <c r="F19" s="2">
+        <v>4330000000</v>
+      </c>
+      <c r="G19" s="2">
         <v>1730000000</v>
       </c>
-      <c r="G19">
+      <c r="H19" s="2">
         <v>789000000</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="2">
         <v>292676000</v>
       </c>
-      <c r="I19">
+      <c r="J19" s="2">
         <v>196957000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
+      <c r="A20" s="2" t="str">
         <v xml:space="preserve">    NET KAR PAYI GELİRİ VEYA GİDERİ</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
+      <c r="A21" s="2" t="str">
         <v xml:space="preserve">    NET ÜCRET VE KOMİSYON GELİRLERİ VEYA GİDERLERİ</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
+        <v>8642000000</v>
+      </c>
+      <c r="C21" s="2">
         <v>5466000000</v>
       </c>
-      <c r="C21">
+      <c r="D21" s="2">
         <v>2490000000</v>
       </c>
-      <c r="D21">
+      <c r="E21" s="2">
         <v>3667938000</v>
       </c>
-      <c r="E21">
-        <v>1115568000</v>
-      </c>
-      <c r="F21">
+      <c r="F21" s="2">
+        <v>1115000000</v>
+      </c>
+      <c r="G21" s="2">
         <v>-2000000</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
         <v>-724000</v>
       </c>
-      <c r="I21">
+      <c r="J21" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
+      <c r="A22" s="2" t="str">
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
+        <v>13312000000</v>
+      </c>
+      <c r="C22" s="2">
         <v>8430000000</v>
       </c>
-      <c r="C22">
+      <c r="D22" s="2">
         <v>3909000000</v>
       </c>
-      <c r="D22">
+      <c r="E22" s="2">
         <v>5563591000</v>
       </c>
-      <c r="E22">
-        <v>1459666000</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
+      <c r="F22" s="2">
+        <v>1459000000</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
+      <c r="A23" s="2" t="str">
         <v xml:space="preserve">    Verilen Ücret ve Komisyonlar (-)</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
+        <v>-4670000000</v>
+      </c>
+      <c r="C23" s="2">
         <v>-2964000000</v>
       </c>
-      <c r="C23">
+      <c r="D23" s="2">
         <v>-1419000000</v>
       </c>
-      <c r="D23">
+      <c r="E23" s="2">
         <v>-1895653000</v>
       </c>
-      <c r="E23">
-        <v>-344098000</v>
-      </c>
-      <c r="F23">
+      <c r="F23" s="2">
+        <v>-344000000</v>
+      </c>
+      <c r="G23" s="2">
         <v>-2000000</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
         <v>-724000</v>
       </c>
-      <c r="I23">
+      <c r="J23" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
+      <c r="A24" s="2" t="str">
         <v xml:space="preserve">    PERSONEL GİDERLERİ (-)</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
+        <v>-2875000000</v>
+      </c>
+      <c r="C24" s="2">
         <v>-1866000000</v>
       </c>
-      <c r="C24">
+      <c r="D24" s="2">
         <v>-910000000</v>
       </c>
-      <c r="D24">
+      <c r="E24" s="2">
         <v>-1070172000</v>
       </c>
-      <c r="E24">
-        <v>-386316000</v>
-      </c>
-      <c r="F24">
+      <c r="F24" s="2">
+        <v>-386000000</v>
+      </c>
+      <c r="G24" s="2">
         <v>-100000000</v>
       </c>
-      <c r="G24">
+      <c r="H24" s="2">
         <v>-44000000</v>
       </c>
-      <c r="H24">
+      <c r="I24" s="2">
         <v>-65830000</v>
       </c>
-      <c r="I24">
+      <c r="J24" s="2">
         <v>-41031000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
+      <c r="A25" s="2" t="str">
         <v xml:space="preserve">    TEMETTÜ GELİRLERİ</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
+      <c r="A26" s="2" t="str">
         <v xml:space="preserve">    TİCARİ KAR VEYA ZARAR (Net)</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
+        <v>-2939000000</v>
+      </c>
+      <c r="C26" s="2">
         <v>-1264000000</v>
       </c>
-      <c r="C26">
+      <c r="D26" s="2">
         <v>-611000000</v>
       </c>
-      <c r="D26">
+      <c r="E26" s="2">
         <v>-1689837000</v>
       </c>
-      <c r="E26">
-        <v>-636078000</v>
-      </c>
-      <c r="F26">
+      <c r="F26" s="2">
+        <v>-637000000</v>
+      </c>
+      <c r="G26" s="2">
         <v>91000000</v>
       </c>
-      <c r="G26">
+      <c r="H26" s="2">
         <v>48000000</v>
       </c>
-      <c r="H26">
+      <c r="I26" s="2">
         <v>1395480000</v>
       </c>
-      <c r="I26">
+      <c r="J26" s="2">
         <v>1131705000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
+      <c r="A27" s="2" t="str">
         <v xml:space="preserve">    Sermaye Piyasası İşlemleri Karı (Zararı)</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="C27" s="2">
         <v>-13000000</v>
       </c>
-      <c r="C27">
+      <c r="D27" s="2">
         <v>-13000000</v>
       </c>
-      <c r="D27">
+      <c r="E27" s="2">
         <v>-57074000</v>
       </c>
-      <c r="E27">
-        <v>675000</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
+      <c r="A28" s="2" t="str">
         <v xml:space="preserve">    Türev Finansal İşlemlerden Kar (Zarar)</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
+        <v>-3991000000</v>
+      </c>
+      <c r="C28" s="2">
         <v>-2015000000</v>
       </c>
-      <c r="C28">
+      <c r="D28" s="2">
         <v>-1048000000</v>
       </c>
-      <c r="D28">
+      <c r="E28" s="2">
         <v>84901000</v>
       </c>
-      <c r="E28">
-        <v>-448863000</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
+      <c r="F28" s="2">
+        <v>-449000000</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
+      <c r="A29" s="2" t="str">
         <v xml:space="preserve">    Kambiyo İşlemleri Karı (Zararı)</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
+        <v>1051000000</v>
+      </c>
+      <c r="C29" s="2">
         <v>764000000</v>
       </c>
-      <c r="C29">
+      <c r="D29" s="2">
         <v>450000000</v>
       </c>
-      <c r="D29">
+      <c r="E29" s="2">
         <v>-1717664000</v>
       </c>
-      <c r="E29">
-        <v>-187890000</v>
-      </c>
-      <c r="F29">
+      <c r="F29" s="2">
+        <v>-188000000</v>
+      </c>
+      <c r="G29" s="2">
         <v>91000000</v>
       </c>
-      <c r="G29">
+      <c r="H29" s="2">
         <v>48000000</v>
       </c>
-      <c r="H29">
+      <c r="I29" s="2">
         <v>1395480000</v>
       </c>
-      <c r="I29">
+      <c r="J29" s="2">
         <v>1131705000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
+      <c r="A30" s="2" t="str">
         <v xml:space="preserve">    DİĞER FAALİYET GELİRLERİ</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
+        <v>1146000000</v>
+      </c>
+      <c r="C30" s="2">
         <v>1168000000</v>
       </c>
-      <c r="C30">
+      <c r="D30" s="2">
         <v>49000000</v>
       </c>
-      <c r="D30">
+      <c r="E30" s="2">
         <v>2689587000</v>
       </c>
-      <c r="E30">
-        <v>2629700000</v>
-      </c>
-      <c r="F30">
+      <c r="F30" s="2">
+        <v>2630000000</v>
+      </c>
+      <c r="G30" s="2">
         <v>1000000</v>
       </c>
-      <c r="G30">
+      <c r="H30" s="2">
         <v>1000000</v>
       </c>
-      <c r="H30">
+      <c r="I30" s="2">
         <v>2065000</v>
       </c>
-      <c r="I30">
+      <c r="J30" s="2">
         <v>60000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
+      <c r="A31" s="2" t="str">
         <v xml:space="preserve">    FAALİYET BRÜT KÂRI</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="2">
+        <v>25455000000</v>
+      </c>
+      <c r="C31" s="2">
         <v>16170000000</v>
       </c>
-      <c r="C31">
+      <c r="D31" s="2">
         <v>7237000000</v>
       </c>
-      <c r="D31">
+      <c r="E31" s="2">
         <v>14443326000</v>
       </c>
-      <c r="E31">
-        <v>7439808000</v>
-      </c>
-      <c r="F31">
+      <c r="F31" s="2">
+        <v>7438000000</v>
+      </c>
+      <c r="G31" s="2">
         <v>1820000000</v>
       </c>
-      <c r="G31">
+      <c r="H31" s="2">
         <v>838000000</v>
       </c>
-      <c r="H31">
+      <c r="I31" s="2">
         <v>1689497000</v>
       </c>
-      <c r="I31">
+      <c r="J31" s="2">
         <v>1328722000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
+      <c r="A32" s="2" t="str">
         <v xml:space="preserve">    Beklenen Zarar Karşılıkları (-)</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="2">
+        <v>-7228000000</v>
+      </c>
+      <c r="C32" s="2">
         <v>-4774000000</v>
       </c>
-      <c r="C32">
+      <c r="D32" s="2">
         <v>-1679000000</v>
       </c>
-      <c r="D32">
+      <c r="E32" s="2">
         <v>-2756632000</v>
       </c>
-      <c r="E32">
-        <v>-865212000</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
+      <c r="F32" s="2">
+        <v>-865000000</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
         <v>-1070000</v>
       </c>
-      <c r="I32">
+      <c r="J32" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
+      <c r="A33" s="2" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="2">
+        <v>-6535000000</v>
+      </c>
+      <c r="C33" s="2">
         <v>-4115000000</v>
       </c>
-      <c r="C33">
+      <c r="D33" s="2">
         <v>-1939000000</v>
       </c>
-      <c r="D33">
+      <c r="E33" s="2">
         <v>-3752865000</v>
       </c>
-      <c r="E33">
-        <v>-1759264000</v>
-      </c>
-      <c r="F33">
+      <c r="F33" s="2">
+        <v>-1759000000</v>
+      </c>
+      <c r="G33" s="2">
         <v>-706000000</v>
       </c>
-      <c r="G33">
+      <c r="H33" s="2">
         <v>-318000000</v>
       </c>
-      <c r="H33">
+      <c r="I33" s="2">
         <v>-775550000</v>
       </c>
-      <c r="I33">
+      <c r="J33" s="2">
         <v>-562172000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
+      <c r="A34" s="2" t="str">
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="2">
+        <v>8815000000</v>
+      </c>
+      <c r="C34" s="2">
         <v>5414000000</v>
       </c>
-      <c r="C34">
+      <c r="D34" s="2">
         <v>2709000000</v>
       </c>
-      <c r="D34">
+      <c r="E34" s="2">
         <v>6863316000</v>
       </c>
-      <c r="E34">
-        <v>4426718000</v>
-      </c>
-      <c r="F34">
+      <c r="F34" s="2">
+        <v>4426000000</v>
+      </c>
+      <c r="G34" s="2">
         <v>1014000000</v>
       </c>
-      <c r="G34">
+      <c r="H34" s="2">
         <v>476000000</v>
       </c>
-      <c r="H34">
+      <c r="I34" s="2">
         <v>847042000</v>
       </c>
-      <c r="I34">
+      <c r="J34" s="2">
         <v>725514000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
+      <c r="A35" s="2" t="str">
         <v xml:space="preserve">    Birleşme İşlemi Sonrasında Gelir Olarak Kaydedilen Fazlalık Tutarı</v>
       </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
+      <c r="A36" s="2" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemi Uygulanan Ortaklıklardan Kar (Zarar))</v>
       </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
+      <c r="A37" s="2" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Karı (Zararı)</v>
       </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
+      <c r="A38" s="2" t="str">
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="2">
+        <v>8815000000</v>
+      </c>
+      <c r="C38" s="2">
         <v>5414000000</v>
       </c>
-      <c r="C38">
+      <c r="D38" s="2">
         <v>2709000000</v>
       </c>
-      <c r="D38">
+      <c r="E38" s="2">
         <v>6863316000</v>
       </c>
-      <c r="E38">
-        <v>4426718000</v>
-      </c>
-      <c r="F38">
+      <c r="F38" s="2">
+        <v>4426000000</v>
+      </c>
+      <c r="G38" s="2">
         <v>1014000000</v>
       </c>
-      <c r="G38">
+      <c r="H38" s="2">
         <v>476000000</v>
       </c>
-      <c r="H38">
+      <c r="I38" s="2">
         <v>847042000</v>
       </c>
-      <c r="I38">
+      <c r="J38" s="2">
         <v>725514000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
+      <c r="A39" s="2" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="2">
+        <v>-2519000000</v>
+      </c>
+      <c r="C39" s="2">
         <v>-1546000000</v>
       </c>
-      <c r="C39">
+      <c r="D39" s="2">
         <v>-788000000</v>
       </c>
-      <c r="D39">
+      <c r="E39" s="2">
         <v>-1207379000</v>
       </c>
-      <c r="E39">
-        <v>-498469000</v>
-      </c>
-      <c r="F39">
+      <c r="F39" s="2">
+        <v>-498000000</v>
+      </c>
+      <c r="G39" s="2">
         <v>-249000000</v>
       </c>
-      <c r="G39">
+      <c r="H39" s="2">
         <v>-106000000</v>
       </c>
-      <c r="H39">
+      <c r="I39" s="2">
         <v>-178587000</v>
       </c>
-      <c r="I39">
+      <c r="J39" s="2">
         <v>-164932000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
+      <c r="A40" s="2" t="str">
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="2">
+        <v>-3212000000</v>
+      </c>
+      <c r="C40" s="2">
         <v>-3362000000</v>
       </c>
-      <c r="C40">
+      <c r="D40" s="2">
         <v>-2045000000</v>
       </c>
-      <c r="D40">
+      <c r="E40" s="2">
         <v>-368957000</v>
       </c>
-      <c r="E40">
-        <v>-6250000</v>
-      </c>
-      <c r="F40">
+      <c r="F40" s="2">
+        <v>-6000000</v>
+      </c>
+      <c r="G40" s="2">
         <v>-293000000</v>
       </c>
-      <c r="G40">
+      <c r="H40" s="2">
         <v>-137000000</v>
       </c>
-      <c r="H40">
+      <c r="I40" s="2">
         <v>-75171000</v>
       </c>
-      <c r="I40">
+      <c r="J40" s="2">
         <v>-77746000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
+      <c r="A41" s="2" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Gider Etkisi</v>
       </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
+      <c r="B41" s="2">
+        <v>0</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
         <v>-838422000</v>
       </c>
-      <c r="E41">
-        <v>-492219000</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
+      <c r="F41" s="2">
+        <v>-492000000</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
         <v>-103416000</v>
       </c>
-      <c r="I41">
+      <c r="J41" s="2">
         <v>-87186000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
+      <c r="A42" s="2" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Gelir Etkisi</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="2">
+        <v>693000000</v>
+      </c>
+      <c r="C42" s="2">
         <v>1816000000</v>
       </c>
-      <c r="C42">
+      <c r="D42" s="2">
         <v>1257000000</v>
       </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42">
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2">
         <v>44000000</v>
       </c>
-      <c r="G42">
+      <c r="H42" s="2">
         <v>31000000</v>
       </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
+      <c r="A43" s="2" t="str">
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="2">
+        <v>6296000000</v>
+      </c>
+      <c r="C43" s="2">
         <v>3868000000</v>
       </c>
-      <c r="C43">
+      <c r="D43" s="2">
         <v>1921000000</v>
       </c>
-      <c r="D43">
+      <c r="E43" s="2">
         <v>5655937000</v>
       </c>
-      <c r="E43">
-        <v>3928249000</v>
-      </c>
-      <c r="F43">
+      <c r="F43" s="2">
+        <v>3928000000</v>
+      </c>
+      <c r="G43" s="2">
         <v>765000000</v>
       </c>
-      <c r="G43">
+      <c r="H43" s="2">
         <v>370000000</v>
       </c>
-      <c r="H43">
+      <c r="I43" s="2">
         <v>668455000</v>
       </c>
-      <c r="I43">
+      <c r="J43" s="2">
         <v>560582000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
+      <c r="A44" s="2" t="str">
         <v xml:space="preserve">    DÖNEM NET KARI VEYA ZARARI</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="2">
+        <v>6296000000</v>
+      </c>
+      <c r="C44" s="2">
         <v>3868000000</v>
       </c>
-      <c r="C44">
+      <c r="D44" s="2">
         <v>1921000000</v>
       </c>
-      <c r="D44">
+      <c r="E44" s="2">
         <v>5655937000</v>
       </c>
-      <c r="E44">
-        <v>3928249000</v>
-      </c>
-      <c r="F44">
+      <c r="F44" s="2">
+        <v>3928000000</v>
+      </c>
+      <c r="G44" s="2">
         <v>765000000</v>
       </c>
-      <c r="G44">
+      <c r="H44" s="2">
         <v>370000000</v>
       </c>
-      <c r="H44">
+      <c r="I44" s="2">
         <v>668455000</v>
       </c>
-      <c r="I44">
+      <c r="J44" s="2">
         <v>560582000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
+      <c r="A45" s="2" t="str">
         <v xml:space="preserve">    Grubun Karı (Zararı)</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="2">
+        <v>6296000000</v>
+      </c>
+      <c r="C45" s="2">
         <v>3868000000</v>
       </c>
-      <c r="C45">
+      <c r="D45" s="2">
         <v>1921000000</v>
       </c>
-      <c r="D45">
+      <c r="E45" s="2">
         <v>5655937000</v>
       </c>
-      <c r="E45">
-        <v>3928249000</v>
-      </c>
-      <c r="F45">
+      <c r="F45" s="2">
+        <v>3928000000</v>
+      </c>
+      <c r="G45" s="2">
         <v>765000000</v>
       </c>
-      <c r="G45">
+      <c r="H45" s="2">
         <v>370000000</v>
       </c>
-      <c r="H45">
+      <c r="I45" s="2">
         <v>668455000</v>
       </c>
-      <c r="I45">
+      <c r="J45" s="2">
         <v>560582000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
+      <c r="A46" s="2" t="str">
         <v xml:space="preserve">    Azınlık Payları Karı (Zararı)</v>
       </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
+      <c r="B46" s="2">
+        <v>0</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+      <c r="J46" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J46"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:J46"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2758,1133 +3054,1260 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="2" t="str">
         <v>Kalem</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" s="2" t="str">
+        <v>2026/9</v>
+      </c>
+      <c r="C1" s="2" t="str">
         <v>2026/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" s="2" t="str">
         <v>2026/3</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" s="2" t="str">
         <v>2025/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" s="2" t="str">
         <v>2025/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" s="2" t="str">
         <v>2025/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" s="2" t="str">
         <v>2025/3</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" s="2" t="str">
         <v>2024/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" s="2" t="str">
         <v>2024/9</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" s="2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3" s="2" t="str">
         <v xml:space="preserve">    FAİZ GELİRLERİ</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
+        <v>21381000000</v>
+      </c>
+      <c r="C3" s="2">
         <v>19433000000</v>
       </c>
-      <c r="C3">
+      <c r="D3" s="2">
         <v>17036000000</v>
       </c>
-      <c r="D3">
-        <v>17502490000</v>
-      </c>
-      <c r="E3">
-        <v>7211834000</v>
-      </c>
-      <c r="F3">
+      <c r="E3" s="2">
+        <v>17503324000</v>
+      </c>
+      <c r="F3" s="2">
+        <v>7211000000</v>
+      </c>
+      <c r="G3" s="2">
         <v>951000000</v>
       </c>
-      <c r="G3">
+      <c r="H3" s="2">
         <v>795000000</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="2">
         <v>95953000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4" s="2" t="str">
         <v xml:space="preserve">    KAR PAYI GELİRİ</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5" s="2" t="str">
         <v xml:space="preserve">    Kredilerden Alınan Faizler</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
+        <v>15175000000</v>
+      </c>
+      <c r="C5" s="2">
         <v>13771000000</v>
       </c>
-      <c r="C5">
+      <c r="D5" s="2">
         <v>12545000000</v>
       </c>
-      <c r="D5">
-        <v>12301557000</v>
-      </c>
-      <c r="E5">
-        <v>4447673000</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="E5" s="2">
+        <v>12301230000</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4448000000</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6" s="2" t="str">
         <v xml:space="preserve">    Zorunlu Karşılıklardan Alınan Faizler</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
+        <v>2619000000</v>
+      </c>
+      <c r="C6" s="2">
         <v>2613000000</v>
       </c>
-      <c r="C6">
+      <c r="D6" s="2">
         <v>2276000000</v>
       </c>
-      <c r="D6">
-        <v>2139521000</v>
-      </c>
-      <c r="E6">
-        <v>882627000</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="E6" s="2">
+        <v>2139148000</v>
+      </c>
+      <c r="F6" s="2">
+        <v>883000000</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
+      <c r="A7" s="2" t="str">
         <v xml:space="preserve">    Bankalardan Alınan Faizler</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
+        <v>340000000</v>
+      </c>
+      <c r="C7" s="2">
         <v>253000000</v>
       </c>
-      <c r="C7">
+      <c r="D7" s="2">
         <v>201000000</v>
       </c>
-      <c r="D7">
-        <v>786800000</v>
-      </c>
-      <c r="E7">
-        <v>1027344000</v>
-      </c>
-      <c r="F7">
+      <c r="E7" s="2">
+        <v>787144000</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1027000000</v>
+      </c>
+      <c r="G7" s="2">
         <v>14000000</v>
       </c>
-      <c r="G7">
+      <c r="H7" s="2">
         <v>311000000</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="2">
         <v>95953000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
+      <c r="A8" s="2" t="str">
         <v xml:space="preserve">    Para Piyasası İşlemlerinden Alınan Faizler</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
         <v>8000000</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>417841000</v>
-      </c>
-      <c r="E8">
-        <v>263159000</v>
-      </c>
-      <c r="F8">
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>418000000</v>
+      </c>
+      <c r="F8" s="2">
+        <v>263000000</v>
+      </c>
+      <c r="G8" s="2">
         <v>925000000</v>
       </c>
-      <c r="G8">
+      <c r="H8" s="2">
         <v>483000000</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9" s="2" t="str">
         <v xml:space="preserve">    Menkul Değerlerden Alınan Faizler</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
+        <v>3245000000</v>
+      </c>
+      <c r="C9" s="2">
         <v>2788000000</v>
       </c>
-      <c r="C9">
+      <c r="D9" s="2">
         <v>2011000000</v>
       </c>
-      <c r="D9">
-        <v>1856755000</v>
-      </c>
-      <c r="E9">
-        <v>591031000</v>
-      </c>
-      <c r="F9">
+      <c r="E9" s="2">
+        <v>1857786000</v>
+      </c>
+      <c r="F9" s="2">
+        <v>590000000</v>
+      </c>
+      <c r="G9" s="2">
         <v>12000000</v>
       </c>
-      <c r="G9">
+      <c r="H9" s="2">
         <v>1000000</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
+      <c r="A10" s="2" t="str">
         <v xml:space="preserve">    Finansal Kiralama Gelirleri</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
+      <c r="A11" s="2" t="str">
         <v xml:space="preserve">    Diğer Faiz Gelirleri</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
+      <c r="B11" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
         <v>3000000</v>
       </c>
-      <c r="D11">
+      <c r="E11" s="2">
         <v>16000</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
+      <c r="A12" s="2" t="str">
         <v xml:space="preserve">    FAİZ GİDERLERİ (-)</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
+        <v>-13575000000</v>
+      </c>
+      <c r="C12" s="2">
         <v>-13942000000</v>
       </c>
-      <c r="C12">
+      <c r="D12" s="2">
         <v>-11727000000</v>
       </c>
-      <c r="D12">
-        <v>-12057470000</v>
-      </c>
-      <c r="E12">
-        <v>-4611216000</v>
-      </c>
-      <c r="F12">
+      <c r="E12" s="2">
+        <v>-12057686000</v>
+      </c>
+      <c r="F12" s="2">
+        <v>-4611000000</v>
+      </c>
+      <c r="G12" s="2">
         <v>-10000000</v>
       </c>
-      <c r="G12">
+      <c r="H12" s="2">
         <v>-6000000</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="2">
         <v>-234000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
+      <c r="A13" s="2" t="str">
         <v xml:space="preserve">    KAR PAYI GİDERLERİ (-)</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
+      <c r="A14" s="2" t="str">
         <v xml:space="preserve">    Mevduata Verilen Faizler</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
+        <v>-13262000000</v>
+      </c>
+      <c r="C14" s="2">
         <v>-13396000000</v>
       </c>
-      <c r="C14">
+      <c r="D14" s="2">
         <v>-11396000000</v>
       </c>
-      <c r="D14">
-        <v>-11916059000</v>
-      </c>
-      <c r="E14">
-        <v>-4607337000</v>
-      </c>
-      <c r="F14">
+      <c r="E14" s="2">
+        <v>-11916396000</v>
+      </c>
+      <c r="F14" s="2">
+        <v>-4607000000</v>
+      </c>
+      <c r="G14" s="2">
         <v>-1000000</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
+      <c r="A15" s="2" t="str">
         <v xml:space="preserve">    Kullanılan Kredilere Verilen Faizler</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
         <v>-1000000</v>
       </c>
-      <c r="D15">
-        <v>562000</v>
-      </c>
-      <c r="E15">
-        <v>-562000</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
+      <c r="E15" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F15" s="2">
+        <v>-1000000</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
         <v>3000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
+      <c r="A16" s="2" t="str">
         <v xml:space="preserve">    Para Piyasası İşlemlerine Verilen Faizler</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
+        <v>-269000000</v>
+      </c>
+      <c r="C16" s="2">
         <v>-499000000</v>
       </c>
-      <c r="C16">
+      <c r="D16" s="2">
         <v>-293000000</v>
       </c>
-      <c r="D16">
-        <v>-110078000</v>
-      </c>
-      <c r="E16">
-        <v>-4000</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
+      <c r="E16" s="2">
+        <v>-110082000</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
+      <c r="A17" s="2" t="str">
         <v xml:space="preserve">    İhraç Edilen Menkul Kıymetlere Verilen Faizler</v>
       </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
+      <c r="A18" s="2" t="str">
         <v xml:space="preserve">    Diğer Faiz Giderleri</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
+        <v>-20000000</v>
+      </c>
+      <c r="C18" s="2">
         <v>-23000000</v>
       </c>
-      <c r="C18">
+      <c r="D18" s="2">
         <v>-7000000</v>
       </c>
-      <c r="D18">
-        <v>-12011000</v>
-      </c>
-      <c r="E18">
-        <v>-1859000</v>
-      </c>
-      <c r="F18">
+      <c r="E18" s="2">
+        <v>-11870000</v>
+      </c>
+      <c r="F18" s="2">
+        <v>-2000000</v>
+      </c>
+      <c r="G18" s="2">
         <v>-7000000</v>
       </c>
-      <c r="G18">
+      <c r="H18" s="2">
         <v>-4000000</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
+      <c r="A19" s="2" t="str">
         <v xml:space="preserve">    NET FAİZ GELİRİ VEYA GİDERİ</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
+        <v>7806000000</v>
+      </c>
+      <c r="C19" s="2">
         <v>5491000000</v>
       </c>
-      <c r="C19">
+      <c r="D19" s="2">
         <v>5309000000</v>
       </c>
-      <c r="D19">
-        <v>5445020000</v>
-      </c>
-      <c r="E19">
-        <v>2600618000</v>
-      </c>
-      <c r="F19">
+      <c r="E19" s="2">
+        <v>5445638000</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2600000000</v>
+      </c>
+      <c r="G19" s="2">
         <v>941000000</v>
       </c>
-      <c r="G19">
+      <c r="H19" s="2">
         <v>789000000</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="2">
         <v>95719000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
+      <c r="A20" s="2" t="str">
         <v xml:space="preserve">    NET KAR PAYI GELİRİ VEYA GİDERİ</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
+      <c r="A21" s="2" t="str">
         <v xml:space="preserve">    NET ÜCRET VE KOMİSYON GELİRLERİ VEYA GİDERLERİ</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
+        <v>3176000000</v>
+      </c>
+      <c r="C21" s="2">
         <v>2976000000</v>
       </c>
-      <c r="C21">
+      <c r="D21" s="2">
         <v>2490000000</v>
       </c>
-      <c r="D21">
-        <v>2552370000</v>
-      </c>
-      <c r="E21">
-        <v>1117568000</v>
-      </c>
-      <c r="F21">
+      <c r="E21" s="2">
+        <v>2552938000</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1117000000</v>
+      </c>
+      <c r="G21" s="2">
         <v>-2000000</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
         <v>-724000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
+      <c r="A22" s="2" t="str">
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
+        <v>4882000000</v>
+      </c>
+      <c r="C22" s="2">
         <v>4521000000</v>
       </c>
-      <c r="C22">
+      <c r="D22" s="2">
         <v>3909000000</v>
       </c>
-      <c r="D22">
-        <v>4103925000</v>
-      </c>
-      <c r="E22">
-        <v>1459666000</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
+      <c r="E22" s="2">
+        <v>4104591000</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1459000000</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
+      <c r="A23" s="2" t="str">
         <v xml:space="preserve">    Verilen Ücret ve Komisyonlar (-)</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
+        <v>-1706000000</v>
+      </c>
+      <c r="C23" s="2">
         <v>-1545000000</v>
       </c>
-      <c r="C23">
+      <c r="D23" s="2">
         <v>-1419000000</v>
       </c>
-      <c r="D23">
-        <v>-1551555000</v>
-      </c>
-      <c r="E23">
-        <v>-342098000</v>
-      </c>
-      <c r="F23">
+      <c r="E23" s="2">
+        <v>-1551653000</v>
+      </c>
+      <c r="F23" s="2">
+        <v>-342000000</v>
+      </c>
+      <c r="G23" s="2">
         <v>-2000000</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
         <v>-724000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
+      <c r="A24" s="2" t="str">
         <v xml:space="preserve">    PERSONEL GİDERLERİ (-)</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
+        <v>-1009000000</v>
+      </c>
+      <c r="C24" s="2">
         <v>-956000000</v>
       </c>
-      <c r="C24">
+      <c r="D24" s="2">
         <v>-910000000</v>
       </c>
-      <c r="D24">
-        <v>-683856000</v>
-      </c>
-      <c r="E24">
-        <v>-286316000</v>
-      </c>
-      <c r="F24">
+      <c r="E24" s="2">
+        <v>-684172000</v>
+      </c>
+      <c r="F24" s="2">
+        <v>-286000000</v>
+      </c>
+      <c r="G24" s="2">
         <v>-56000000</v>
       </c>
-      <c r="G24">
+      <c r="H24" s="2">
         <v>-44000000</v>
       </c>
-      <c r="H24">
+      <c r="I24" s="2">
         <v>-24799000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
+      <c r="A25" s="2" t="str">
         <v xml:space="preserve">    TEMETTÜ GELİRLERİ</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
+      <c r="A26" s="2" t="str">
         <v xml:space="preserve">    TİCARİ KAR VEYA ZARAR (Net)</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
+        <v>-1675000000</v>
+      </c>
+      <c r="C26" s="2">
         <v>-653000000</v>
       </c>
-      <c r="C26">
+      <c r="D26" s="2">
         <v>-611000000</v>
       </c>
-      <c r="D26">
-        <v>-1053759000</v>
-      </c>
-      <c r="E26">
-        <v>-727078000</v>
-      </c>
-      <c r="F26">
+      <c r="E26" s="2">
+        <v>-1052837000</v>
+      </c>
+      <c r="F26" s="2">
+        <v>-728000000</v>
+      </c>
+      <c r="G26" s="2">
         <v>43000000</v>
       </c>
-      <c r="G26">
+      <c r="H26" s="2">
         <v>48000000</v>
       </c>
-      <c r="H26">
+      <c r="I26" s="2">
         <v>263775000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
+      <c r="A27" s="2" t="str">
         <v xml:space="preserve">    Sermaye Piyasası İşlemleri Karı (Zararı)</v>
       </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-      <c r="C27">
+      <c r="B27" s="2">
+        <v>14000000</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
         <v>-13000000</v>
       </c>
-      <c r="D27">
-        <v>-57749000</v>
-      </c>
-      <c r="E27">
-        <v>675000</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
+      <c r="E27" s="2">
+        <v>-57074000</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
+      <c r="A28" s="2" t="str">
         <v xml:space="preserve">    Türev Finansal İşlemlerden Kar (Zarar)</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
+        <v>-1976000000</v>
+      </c>
+      <c r="C28" s="2">
         <v>-967000000</v>
       </c>
-      <c r="C28">
+      <c r="D28" s="2">
         <v>-1048000000</v>
       </c>
-      <c r="D28">
-        <v>533764000</v>
-      </c>
-      <c r="E28">
-        <v>-448863000</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
+      <c r="E28" s="2">
+        <v>533901000</v>
+      </c>
+      <c r="F28" s="2">
+        <v>-449000000</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
+      <c r="A29" s="2" t="str">
         <v xml:space="preserve">    Kambiyo İşlemleri Karı (Zararı)</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
+        <v>287000000</v>
+      </c>
+      <c r="C29" s="2">
         <v>314000000</v>
       </c>
-      <c r="C29">
+      <c r="D29" s="2">
         <v>450000000</v>
       </c>
-      <c r="D29">
-        <v>-1529774000</v>
-      </c>
-      <c r="E29">
-        <v>-278890000</v>
-      </c>
-      <c r="F29">
+      <c r="E29" s="2">
+        <v>-1529664000</v>
+      </c>
+      <c r="F29" s="2">
+        <v>-279000000</v>
+      </c>
+      <c r="G29" s="2">
         <v>43000000</v>
       </c>
-      <c r="G29">
+      <c r="H29" s="2">
         <v>48000000</v>
       </c>
-      <c r="H29">
+      <c r="I29" s="2">
         <v>263775000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
+      <c r="A30" s="2" t="str">
         <v xml:space="preserve">    DİĞER FAALİYET GELİRLERİ</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
+        <v>-22000000</v>
+      </c>
+      <c r="C30" s="2">
         <v>1119000000</v>
       </c>
-      <c r="C30">
+      <c r="D30" s="2">
         <v>49000000</v>
       </c>
-      <c r="D30">
-        <v>59887000</v>
-      </c>
-      <c r="E30">
-        <v>2628700000</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
+      <c r="E30" s="2">
+        <v>59587000</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2629000000</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
         <v>1000000</v>
       </c>
-      <c r="H30">
+      <c r="I30" s="2">
         <v>2005000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
+      <c r="A31" s="2" t="str">
         <v xml:space="preserve">    FAALİYET BRÜT KÂRI</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="2">
+        <v>9285000000</v>
+      </c>
+      <c r="C31" s="2">
         <v>8933000000</v>
       </c>
-      <c r="C31">
+      <c r="D31" s="2">
         <v>7237000000</v>
       </c>
-      <c r="D31">
-        <v>7003518000</v>
-      </c>
-      <c r="E31">
-        <v>5619808000</v>
-      </c>
-      <c r="F31">
+      <c r="E31" s="2">
+        <v>7005326000</v>
+      </c>
+      <c r="F31" s="2">
+        <v>5618000000</v>
+      </c>
+      <c r="G31" s="2">
         <v>982000000</v>
       </c>
-      <c r="G31">
+      <c r="H31" s="2">
         <v>838000000</v>
       </c>
-      <c r="H31">
+      <c r="I31" s="2">
         <v>360775000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
+      <c r="A32" s="2" t="str">
         <v xml:space="preserve">    Beklenen Zarar Karşılıkları (-)</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="2">
+        <v>-2454000000</v>
+      </c>
+      <c r="C32" s="2">
         <v>-3095000000</v>
       </c>
-      <c r="C32">
+      <c r="D32" s="2">
         <v>-1679000000</v>
       </c>
-      <c r="D32">
-        <v>-1891420000</v>
-      </c>
-      <c r="E32">
-        <v>-865212000</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
+      <c r="E32" s="2">
+        <v>-1891632000</v>
+      </c>
+      <c r="F32" s="2">
+        <v>-865000000</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
         <v>-1070000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
+      <c r="A33" s="2" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="2">
+        <v>-2420000000</v>
+      </c>
+      <c r="C33" s="2">
         <v>-2176000000</v>
       </c>
-      <c r="C33">
+      <c r="D33" s="2">
         <v>-1939000000</v>
       </c>
-      <c r="D33">
-        <v>-1993601000</v>
-      </c>
-      <c r="E33">
-        <v>-1053264000</v>
-      </c>
-      <c r="F33">
+      <c r="E33" s="2">
+        <v>-1993865000</v>
+      </c>
+      <c r="F33" s="2">
+        <v>-1053000000</v>
+      </c>
+      <c r="G33" s="2">
         <v>-388000000</v>
       </c>
-      <c r="G33">
+      <c r="H33" s="2">
         <v>-318000000</v>
       </c>
-      <c r="H33">
+      <c r="I33" s="2">
         <v>-213378000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
+      <c r="A34" s="2" t="str">
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="2">
+        <v>3401000000</v>
+      </c>
+      <c r="C34" s="2">
         <v>2705000000</v>
       </c>
-      <c r="C34">
+      <c r="D34" s="2">
         <v>2709000000</v>
       </c>
-      <c r="D34">
-        <v>2436598000</v>
-      </c>
-      <c r="E34">
-        <v>3412718000</v>
-      </c>
-      <c r="F34">
+      <c r="E34" s="2">
+        <v>2437316000</v>
+      </c>
+      <c r="F34" s="2">
+        <v>3412000000</v>
+      </c>
+      <c r="G34" s="2">
         <v>538000000</v>
       </c>
-      <c r="G34">
+      <c r="H34" s="2">
         <v>476000000</v>
       </c>
-      <c r="H34">
+      <c r="I34" s="2">
         <v>121528000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
+      <c r="A35" s="2" t="str">
         <v xml:space="preserve">    Birleşme İşlemi Sonrasında Gelir Olarak Kaydedilen Fazlalık Tutarı</v>
       </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
+      <c r="A36" s="2" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemi Uygulanan Ortaklıklardan Kar (Zarar))</v>
       </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
+      <c r="A37" s="2" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Karı (Zararı)</v>
       </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
+      <c r="A38" s="2" t="str">
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="2">
+        <v>3401000000</v>
+      </c>
+      <c r="C38" s="2">
         <v>2705000000</v>
       </c>
-      <c r="C38">
+      <c r="D38" s="2">
         <v>2709000000</v>
       </c>
-      <c r="D38">
-        <v>2436598000</v>
-      </c>
-      <c r="E38">
-        <v>3412718000</v>
-      </c>
-      <c r="F38">
+      <c r="E38" s="2">
+        <v>2437316000</v>
+      </c>
+      <c r="F38" s="2">
+        <v>3412000000</v>
+      </c>
+      <c r="G38" s="2">
         <v>538000000</v>
       </c>
-      <c r="G38">
+      <c r="H38" s="2">
         <v>476000000</v>
       </c>
-      <c r="H38">
+      <c r="I38" s="2">
         <v>121528000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
+      <c r="A39" s="2" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="2">
+        <v>-973000000</v>
+      </c>
+      <c r="C39" s="2">
         <v>-758000000</v>
       </c>
-      <c r="C39">
+      <c r="D39" s="2">
         <v>-788000000</v>
       </c>
-      <c r="D39">
-        <v>-708910000</v>
-      </c>
-      <c r="E39">
-        <v>-249469000</v>
-      </c>
-      <c r="F39">
+      <c r="E39" s="2">
+        <v>-709379000</v>
+      </c>
+      <c r="F39" s="2">
+        <v>-249000000</v>
+      </c>
+      <c r="G39" s="2">
         <v>-143000000</v>
       </c>
-      <c r="G39">
+      <c r="H39" s="2">
         <v>-106000000</v>
       </c>
-      <c r="H39">
+      <c r="I39" s="2">
         <v>-13655000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
+      <c r="A40" s="2" t="str">
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="2">
+        <v>150000000</v>
+      </c>
+      <c r="C40" s="2">
         <v>-1317000000</v>
       </c>
-      <c r="C40">
+      <c r="D40" s="2">
         <v>-2045000000</v>
       </c>
-      <c r="D40">
-        <v>-362707000</v>
-      </c>
-      <c r="E40">
-        <v>286750000</v>
-      </c>
-      <c r="F40">
+      <c r="E40" s="2">
+        <v>-362957000</v>
+      </c>
+      <c r="F40" s="2">
+        <v>287000000</v>
+      </c>
+      <c r="G40" s="2">
         <v>-156000000</v>
       </c>
-      <c r="G40">
+      <c r="H40" s="2">
         <v>-137000000</v>
       </c>
-      <c r="H40">
+      <c r="I40" s="2">
         <v>2575000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
+      <c r="A41" s="2" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Gider Etkisi</v>
       </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>-346203000</v>
-      </c>
-      <c r="E41">
-        <v>-492219000</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
+      <c r="B41" s="2">
+        <v>0</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
+        <v>-346422000</v>
+      </c>
+      <c r="F41" s="2">
+        <v>-492000000</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
         <v>-16230000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
+      <c r="A42" s="2" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Gelir Etkisi</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="2">
+        <v>-1123000000</v>
+      </c>
+      <c r="C42" s="2">
         <v>559000000</v>
       </c>
-      <c r="C42">
+      <c r="D42" s="2">
         <v>1257000000</v>
       </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42">
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
         <v>-44000000</v>
       </c>
-      <c r="F42">
+      <c r="G42" s="2">
         <v>13000000</v>
       </c>
-      <c r="G42">
+      <c r="H42" s="2">
         <v>31000000</v>
       </c>
-      <c r="H42">
+      <c r="I42" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
+      <c r="A43" s="2" t="str">
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="2">
+        <v>2428000000</v>
+      </c>
+      <c r="C43" s="2">
         <v>1947000000</v>
       </c>
-      <c r="C43">
+      <c r="D43" s="2">
         <v>1921000000</v>
       </c>
-      <c r="D43">
-        <v>1727688000</v>
-      </c>
-      <c r="E43">
-        <v>3163249000</v>
-      </c>
-      <c r="F43">
+      <c r="E43" s="2">
+        <v>1727937000</v>
+      </c>
+      <c r="F43" s="2">
+        <v>3163000000</v>
+      </c>
+      <c r="G43" s="2">
         <v>395000000</v>
       </c>
-      <c r="G43">
+      <c r="H43" s="2">
         <v>370000000</v>
       </c>
-      <c r="H43">
+      <c r="I43" s="2">
         <v>107873000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
+      <c r="A44" s="2" t="str">
         <v xml:space="preserve">    DÖNEM NET KARI VEYA ZARARI</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="2">
+        <v>2428000000</v>
+      </c>
+      <c r="C44" s="2">
         <v>1947000000</v>
       </c>
-      <c r="C44">
+      <c r="D44" s="2">
         <v>1921000000</v>
       </c>
-      <c r="D44">
-        <v>1727688000</v>
-      </c>
-      <c r="E44">
-        <v>3163249000</v>
-      </c>
-      <c r="F44">
+      <c r="E44" s="2">
+        <v>1727937000</v>
+      </c>
+      <c r="F44" s="2">
+        <v>3163000000</v>
+      </c>
+      <c r="G44" s="2">
         <v>395000000</v>
       </c>
-      <c r="G44">
+      <c r="H44" s="2">
         <v>370000000</v>
       </c>
-      <c r="H44">
+      <c r="I44" s="2">
         <v>107873000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
+      <c r="A45" s="2" t="str">
         <v xml:space="preserve">    Grubun Karı (Zararı)</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="2">
+        <v>2428000000</v>
+      </c>
+      <c r="C45" s="2">
         <v>1947000000</v>
       </c>
-      <c r="C45">
+      <c r="D45" s="2">
         <v>1921000000</v>
       </c>
-      <c r="D45">
-        <v>1727688000</v>
-      </c>
-      <c r="E45">
-        <v>3163249000</v>
-      </c>
-      <c r="F45">
+      <c r="E45" s="2">
+        <v>1727937000</v>
+      </c>
+      <c r="F45" s="2">
+        <v>3163000000</v>
+      </c>
+      <c r="G45" s="2">
         <v>395000000</v>
       </c>
-      <c r="G45">
+      <c r="H45" s="2">
         <v>370000000</v>
       </c>
-      <c r="H45">
+      <c r="I45" s="2">
         <v>107873000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
+      <c r="A46" s="2" t="str">
         <v xml:space="preserve">    Azınlık Payları Karı (Zararı)</v>
       </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
+      <c r="B46" s="2">
+        <v>0</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J46"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:J46"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3895,880 +4318,1007 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="2" t="str">
         <v>Kalem</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" s="2" t="str">
+        <v>2026/9</v>
+      </c>
+      <c r="C1" s="2" t="str">
         <v>2026/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" s="2" t="str">
         <v>2026/3</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" s="2" t="str">
         <v>2025/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" s="2" t="str">
         <v>2025/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" s="2" t="str">
         <v>2025/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" s="2" t="str">
         <v>2025/3</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" s="2" t="str">
         <v>2024/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" s="2" t="str">
         <v>2024/9</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" s="2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3" s="2" t="str">
         <v xml:space="preserve">    FAİZ GELİRLERİ</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
+        <v>75353324000</v>
+      </c>
+      <c r="C3" s="2">
         <v>61183324000</v>
       </c>
-      <c r="C3">
+      <c r="D3" s="2">
         <v>42701324000</v>
       </c>
-      <c r="D3">
+      <c r="E3" s="2">
         <v>26460324000</v>
       </c>
-      <c r="E3">
-        <v>9053787000</v>
-      </c>
-      <c r="H3">
+      <c r="F3" s="2">
+        <v>9052953000</v>
+      </c>
+      <c r="I3" s="2">
         <v>296810000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4" s="2" t="str">
         <v xml:space="preserve">    KAR PAYI GELİRİ</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5" s="2" t="str">
         <v xml:space="preserve">    Kredilerden Alınan Faizler</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
+        <v>53792230000</v>
+      </c>
+      <c r="C5" s="2">
         <v>43065230000</v>
       </c>
-      <c r="C5">
+      <c r="D5" s="2">
         <v>29294230000</v>
       </c>
-      <c r="D5">
+      <c r="E5" s="2">
         <v>16749230000</v>
       </c>
-      <c r="E5">
-        <v>4447673000</v>
-      </c>
-      <c r="H5">
+      <c r="F5" s="2">
+        <v>4448000000</v>
+      </c>
+      <c r="I5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6" s="2" t="str">
         <v xml:space="preserve">    Zorunlu Karşılıklardan Alınan Faizler</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
+        <v>9647148000</v>
+      </c>
+      <c r="C6" s="2">
         <v>7911148000</v>
       </c>
-      <c r="C6">
+      <c r="D6" s="2">
         <v>5298148000</v>
       </c>
-      <c r="D6">
+      <c r="E6" s="2">
         <v>3022148000</v>
       </c>
-      <c r="E6">
-        <v>882627000</v>
-      </c>
-      <c r="H6">
+      <c r="F6" s="2">
+        <v>883000000</v>
+      </c>
+      <c r="I6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
+      <c r="A7" s="2" t="str">
         <v xml:space="preserve">    Bankalardan Alınan Faizler</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
+        <v>1581144000</v>
+      </c>
+      <c r="C7" s="2">
         <v>2268144000</v>
       </c>
-      <c r="C7">
+      <c r="D7" s="2">
         <v>2029144000</v>
       </c>
-      <c r="D7">
+      <c r="E7" s="2">
         <v>2139144000</v>
       </c>
-      <c r="E7">
-        <v>1448297000</v>
-      </c>
-      <c r="H7">
+      <c r="F7" s="2">
+        <v>1447953000</v>
+      </c>
+      <c r="I7" s="2">
         <v>181219000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
+      <c r="A8" s="2" t="str">
         <v xml:space="preserve">    Para Piyasası İşlemlerinden Alınan Faizler</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
+        <v>426000000</v>
+      </c>
+      <c r="C8" s="2">
         <v>689000000</v>
       </c>
-      <c r="C8">
+      <c r="D8" s="2">
         <v>1606000000</v>
       </c>
-      <c r="D8">
+      <c r="E8" s="2">
         <v>2089000000</v>
       </c>
-      <c r="E8">
-        <v>1671159000</v>
-      </c>
-      <c r="H8">
+      <c r="F8" s="2">
+        <v>1671000000</v>
+      </c>
+      <c r="I8" s="2">
         <v>115591000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9" s="2" t="str">
         <v xml:space="preserve">    Menkul Değerlerden Alınan Faizler</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
+        <v>9901786000</v>
+      </c>
+      <c r="C9" s="2">
         <v>7246786000</v>
       </c>
-      <c r="C9">
+      <c r="D9" s="2">
         <v>4470786000</v>
       </c>
-      <c r="D9">
+      <c r="E9" s="2">
         <v>2460786000</v>
       </c>
-      <c r="E9">
-        <v>604031000</v>
-      </c>
-      <c r="H9">
+      <c r="F9" s="2">
+        <v>603000000</v>
+      </c>
+      <c r="I9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
+      <c r="A10" s="2" t="str">
         <v xml:space="preserve">    Finansal Kiralama Gelirleri</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
+      <c r="A11" s="2" t="str">
         <v xml:space="preserve">    Diğer Faiz Gelirleri</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
+        <v>5016000</v>
+      </c>
+      <c r="C11" s="2">
         <v>3016000</v>
       </c>
-      <c r="C11">
+      <c r="D11" s="2">
         <v>3016000</v>
       </c>
-      <c r="D11">
+      <c r="E11" s="2">
         <v>16000</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
+      <c r="A12" s="2" t="str">
         <v xml:space="preserve">    FAİZ GİDERLERİ (-)</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
+        <v>-51301686000</v>
+      </c>
+      <c r="C12" s="2">
         <v>-42337686000</v>
       </c>
-      <c r="C12">
+      <c r="D12" s="2">
         <v>-28405686000</v>
       </c>
-      <c r="D12">
+      <c r="E12" s="2">
         <v>-16684686000</v>
       </c>
-      <c r="E12">
-        <v>-4627450000</v>
-      </c>
-      <c r="H12">
+      <c r="F12" s="2">
+        <v>-4627234000</v>
+      </c>
+      <c r="I12" s="2">
         <v>-4134000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
+      <c r="A13" s="2" t="str">
         <v xml:space="preserve">    KAR PAYI GİDERLERİ (-)</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
+      <c r="A14" s="2" t="str">
         <v xml:space="preserve">    Mevduata Verilen Faizler</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
+        <v>-49970396000</v>
+      </c>
+      <c r="C14" s="2">
         <v>-41315396000</v>
       </c>
-      <c r="C14">
+      <c r="D14" s="2">
         <v>-27920396000</v>
       </c>
-      <c r="D14">
+      <c r="E14" s="2">
         <v>-16524396000</v>
       </c>
-      <c r="E14">
-        <v>-4608337000</v>
-      </c>
-      <c r="H14">
+      <c r="F14" s="2">
+        <v>-4608000000</v>
+      </c>
+      <c r="I14" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
+      <c r="A15" s="2" t="str">
         <v xml:space="preserve">    Kullanılan Kredilere Verilen Faizler</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
         <v>-1000000</v>
       </c>
-      <c r="C15">
+      <c r="D15" s="2">
         <v>-1000000</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>-559000</v>
-      </c>
-      <c r="H15">
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>-997000</v>
+      </c>
+      <c r="I15" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
+      <c r="A16" s="2" t="str">
         <v xml:space="preserve">    Para Piyasası İşlemlerine Verilen Faizler</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
+        <v>-1171082000</v>
+      </c>
+      <c r="C16" s="2">
         <v>-902082000</v>
       </c>
-      <c r="C16">
+      <c r="D16" s="2">
         <v>-403082000</v>
       </c>
-      <c r="D16">
+      <c r="E16" s="2">
         <v>-110082000</v>
       </c>
-      <c r="E16">
-        <v>-4000</v>
-      </c>
-      <c r="H16">
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
+      <c r="A17" s="2" t="str">
         <v xml:space="preserve">    İhraç Edilen Menkul Kıymetlere Verilen Faizler</v>
       </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="H17">
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
+      <c r="A18" s="2" t="str">
         <v xml:space="preserve">    Diğer Faiz Giderleri</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
+        <v>-61870000</v>
+      </c>
+      <c r="C18" s="2">
         <v>-43870000</v>
       </c>
-      <c r="C18">
+      <c r="D18" s="2">
         <v>-27870000</v>
       </c>
-      <c r="D18">
+      <c r="E18" s="2">
         <v>-24870000</v>
       </c>
-      <c r="E18">
-        <v>-12859000</v>
-      </c>
-      <c r="H18">
+      <c r="F18" s="2">
+        <v>-13000000</v>
+      </c>
+      <c r="I18" s="2">
         <v>-3525000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
+      <c r="A19" s="2" t="str">
         <v xml:space="preserve">    NET FAİZ GELİRİ VEYA GİDERİ</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
+        <v>24051638000</v>
+      </c>
+      <c r="C19" s="2">
         <v>18845638000</v>
       </c>
-      <c r="C19">
+      <c r="D19" s="2">
         <v>14295638000</v>
       </c>
-      <c r="D19">
+      <c r="E19" s="2">
         <v>9775638000</v>
       </c>
-      <c r="E19">
-        <v>4426337000</v>
-      </c>
-      <c r="H19">
+      <c r="F19" s="2">
+        <v>4425719000</v>
+      </c>
+      <c r="I19" s="2">
         <v>292676000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
+      <c r="A20" s="2" t="str">
         <v xml:space="preserve">    NET KAR PAYI GELİRİ VEYA GİDERİ</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
+      <c r="A21" s="2" t="str">
         <v xml:space="preserve">    NET ÜCRET VE KOMİSYON GELİRLERİ VEYA GİDERLERİ</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
+        <v>11194938000</v>
+      </c>
+      <c r="C21" s="2">
         <v>9135938000</v>
       </c>
-      <c r="C21">
+      <c r="D21" s="2">
         <v>6157938000</v>
       </c>
-      <c r="D21">
+      <c r="E21" s="2">
         <v>3667938000</v>
       </c>
-      <c r="E21">
-        <v>1114844000</v>
-      </c>
-      <c r="H21">
+      <c r="F21" s="2">
+        <v>1114276000</v>
+      </c>
+      <c r="I21" s="2">
         <v>-724000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
+      <c r="A22" s="2" t="str">
         <v xml:space="preserve">    Alınan Ücret ve Komisyonlar</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
+        <v>17416591000</v>
+      </c>
+      <c r="C22" s="2">
         <v>13993591000</v>
       </c>
-      <c r="C22">
+      <c r="D22" s="2">
         <v>9472591000</v>
       </c>
-      <c r="D22">
+      <c r="E22" s="2">
         <v>5563591000</v>
       </c>
-      <c r="E22">
-        <v>1459666000</v>
-      </c>
-      <c r="H22">
+      <c r="F22" s="2">
+        <v>1459000000</v>
+      </c>
+      <c r="I22" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
+      <c r="A23" s="2" t="str">
         <v xml:space="preserve">    Verilen Ücret ve Komisyonlar (-)</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
+        <v>-6221653000</v>
+      </c>
+      <c r="C23" s="2">
         <v>-4857653000</v>
       </c>
-      <c r="C23">
+      <c r="D23" s="2">
         <v>-3314653000</v>
       </c>
-      <c r="D23">
+      <c r="E23" s="2">
         <v>-1895653000</v>
       </c>
-      <c r="E23">
-        <v>-344822000</v>
-      </c>
-      <c r="H23">
+      <c r="F23" s="2">
+        <v>-344724000</v>
+      </c>
+      <c r="I23" s="2">
         <v>-724000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
+      <c r="A24" s="2" t="str">
         <v xml:space="preserve">    PERSONEL GİDERLERİ (-)</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
+        <v>-3559172000</v>
+      </c>
+      <c r="C24" s="2">
         <v>-2836172000</v>
       </c>
-      <c r="C24">
+      <c r="D24" s="2">
         <v>-1936172000</v>
       </c>
-      <c r="D24">
+      <c r="E24" s="2">
         <v>-1070172000</v>
       </c>
-      <c r="E24">
-        <v>-411115000</v>
-      </c>
-      <c r="H24">
+      <c r="F24" s="2">
+        <v>-410799000</v>
+      </c>
+      <c r="I24" s="2">
         <v>-65830000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
+      <c r="A25" s="2" t="str">
         <v xml:space="preserve">    TEMETTÜ GELİRLERİ</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="H25">
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
+      <c r="A26" s="2" t="str">
         <v xml:space="preserve">    TİCARİ KAR VEYA ZARAR (Net)</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
+        <v>-3991837000</v>
+      </c>
+      <c r="C26" s="2">
         <v>-3044837000</v>
       </c>
-      <c r="C26">
+      <c r="D26" s="2">
         <v>-2348837000</v>
       </c>
-      <c r="D26">
+      <c r="E26" s="2">
         <v>-1689837000</v>
       </c>
-      <c r="E26">
-        <v>-372303000</v>
-      </c>
-      <c r="H26">
+      <c r="F26" s="2">
+        <v>-373225000</v>
+      </c>
+      <c r="I26" s="2">
         <v>1395480000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
+      <c r="A27" s="2" t="str">
         <v xml:space="preserve">    Sermaye Piyasası İşlemleri Karı (Zararı)</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
+        <v>-56074000</v>
+      </c>
+      <c r="C27" s="2">
         <v>-70074000</v>
       </c>
-      <c r="C27">
+      <c r="D27" s="2">
         <v>-70074000</v>
       </c>
-      <c r="D27">
+      <c r="E27" s="2">
         <v>-57074000</v>
       </c>
-      <c r="E27">
-        <v>675000</v>
-      </c>
-      <c r="H27">
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
+      <c r="A28" s="2" t="str">
         <v xml:space="preserve">    Türev Finansal İşlemlerden Kar (Zarar)</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
+        <v>-3457099000</v>
+      </c>
+      <c r="C28" s="2">
         <v>-1930099000</v>
       </c>
-      <c r="C28">
+      <c r="D28" s="2">
         <v>-963099000</v>
       </c>
-      <c r="D28">
+      <c r="E28" s="2">
         <v>84901000</v>
       </c>
-      <c r="E28">
-        <v>-448863000</v>
-      </c>
-      <c r="H28">
+      <c r="F28" s="2">
+        <v>-449000000</v>
+      </c>
+      <c r="I28" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
+      <c r="A29" s="2" t="str">
         <v xml:space="preserve">    Kambiyo İşlemleri Karı (Zararı)</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
+        <v>-478664000</v>
+      </c>
+      <c r="C29" s="2">
         <v>-1044664000</v>
       </c>
-      <c r="C29">
+      <c r="D29" s="2">
         <v>-1315664000</v>
       </c>
-      <c r="D29">
+      <c r="E29" s="2">
         <v>-1717664000</v>
       </c>
-      <c r="E29">
-        <v>75885000</v>
-      </c>
-      <c r="H29">
+      <c r="F29" s="2">
+        <v>75775000</v>
+      </c>
+      <c r="I29" s="2">
         <v>1395480000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
+      <c r="A30" s="2" t="str">
         <v xml:space="preserve">    DİĞER FAALİYET GELİRLERİ</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
+        <v>1205587000</v>
+      </c>
+      <c r="C30" s="2">
         <v>3856587000</v>
       </c>
-      <c r="C30">
+      <c r="D30" s="2">
         <v>2737587000</v>
       </c>
-      <c r="D30">
+      <c r="E30" s="2">
         <v>2689587000</v>
       </c>
-      <c r="E30">
-        <v>2631705000</v>
-      </c>
-      <c r="H30">
+      <c r="F30" s="2">
+        <v>2632005000</v>
+      </c>
+      <c r="I30" s="2">
         <v>2065000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
+      <c r="A31" s="2" t="str">
         <v xml:space="preserve">    FAALİYET BRÜT KÂRI</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="2">
+        <v>32460326000</v>
+      </c>
+      <c r="C31" s="2">
         <v>28793326000</v>
       </c>
-      <c r="C31">
+      <c r="D31" s="2">
         <v>20842326000</v>
       </c>
-      <c r="D31">
+      <c r="E31" s="2">
         <v>14443326000</v>
       </c>
-      <c r="E31">
-        <v>7800583000</v>
-      </c>
-      <c r="H31">
+      <c r="F31" s="2">
+        <v>7798775000</v>
+      </c>
+      <c r="I31" s="2">
         <v>1689497000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
+      <c r="A32" s="2" t="str">
         <v xml:space="preserve">    Beklenen Zarar Karşılıkları (-)</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="2">
+        <v>-9119632000</v>
+      </c>
+      <c r="C32" s="2">
         <v>-7530632000</v>
       </c>
-      <c r="C32">
+      <c r="D32" s="2">
         <v>-4435632000</v>
       </c>
-      <c r="D32">
+      <c r="E32" s="2">
         <v>-2756632000</v>
       </c>
-      <c r="E32">
-        <v>-866282000</v>
-      </c>
-      <c r="H32">
+      <c r="F32" s="2">
+        <v>-866070000</v>
+      </c>
+      <c r="I32" s="2">
         <v>-1070000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
+      <c r="A33" s="2" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="2">
+        <v>-8528865000</v>
+      </c>
+      <c r="C33" s="2">
         <v>-7161865000</v>
       </c>
-      <c r="C33">
+      <c r="D33" s="2">
         <v>-5373865000</v>
       </c>
-      <c r="D33">
+      <c r="E33" s="2">
         <v>-3752865000</v>
       </c>
-      <c r="E33">
-        <v>-1972642000</v>
-      </c>
-      <c r="H33">
+      <c r="F33" s="2">
+        <v>-1972378000</v>
+      </c>
+      <c r="I33" s="2">
         <v>-775550000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
+      <c r="A34" s="2" t="str">
         <v xml:space="preserve">    NET FAALİYET KARI (ZARARI)</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="2">
+        <v>11252316000</v>
+      </c>
+      <c r="C34" s="2">
         <v>11263316000</v>
       </c>
-      <c r="C34">
+      <c r="D34" s="2">
         <v>9096316000</v>
       </c>
-      <c r="D34">
+      <c r="E34" s="2">
         <v>6863316000</v>
       </c>
-      <c r="E34">
-        <v>4548246000</v>
-      </c>
-      <c r="H34">
+      <c r="F34" s="2">
+        <v>4547528000</v>
+      </c>
+      <c r="I34" s="2">
         <v>847042000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
+      <c r="A35" s="2" t="str">
         <v xml:space="preserve">    Birleşme İşlemi Sonrasında Gelir Olarak Kaydedilen Fazlalık Tutarı</v>
       </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="H35">
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
+      <c r="A36" s="2" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemi Uygulanan Ortaklıklardan Kar (Zarar))</v>
       </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="H36">
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
+      <c r="A37" s="2" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Karı (Zararı)</v>
       </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="H37">
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
+      <c r="A38" s="2" t="str">
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER VERGİ ÖNCESİ KARI (ZARARI)</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="2">
+        <v>11252316000</v>
+      </c>
+      <c r="C38" s="2">
         <v>11263316000</v>
       </c>
-      <c r="C38">
+      <c r="D38" s="2">
         <v>9096316000</v>
       </c>
-      <c r="D38">
+      <c r="E38" s="2">
         <v>6863316000</v>
       </c>
-      <c r="E38">
-        <v>4548246000</v>
-      </c>
-      <c r="H38">
+      <c r="F38" s="2">
+        <v>4547528000</v>
+      </c>
+      <c r="I38" s="2">
         <v>847042000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
+      <c r="A39" s="2" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Karşılığı (+/-)</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="2">
+        <v>-3228379000</v>
+      </c>
+      <c r="C39" s="2">
         <v>-2504379000</v>
       </c>
-      <c r="C39">
+      <c r="D39" s="2">
         <v>-1889379000</v>
       </c>
-      <c r="D39">
+      <c r="E39" s="2">
         <v>-1207379000</v>
       </c>
-      <c r="E39">
-        <v>-512124000</v>
-      </c>
-      <c r="H39">
+      <c r="F39" s="2">
+        <v>-511655000</v>
+      </c>
+      <c r="I39" s="2">
         <v>-178587000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
+      <c r="A40" s="2" t="str">
         <v xml:space="preserve">    Cari Vergi Karşılığı</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="2">
+        <v>-3574957000</v>
+      </c>
+      <c r="C40" s="2">
         <v>-3437957000</v>
       </c>
-      <c r="C40">
+      <c r="D40" s="2">
         <v>-2276957000</v>
       </c>
-      <c r="D40">
+      <c r="E40" s="2">
         <v>-368957000</v>
       </c>
-      <c r="E40">
-        <v>-3675000</v>
-      </c>
-      <c r="H40">
+      <c r="F40" s="2">
+        <v>-3425000</v>
+      </c>
+      <c r="I40" s="2">
         <v>-75171000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
+      <c r="A41" s="2" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Gider Etkisi</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="2">
+        <v>-346422000</v>
+      </c>
+      <c r="C41" s="2">
         <v>-838422000</v>
       </c>
-      <c r="C41">
+      <c r="D41" s="2">
         <v>-838422000</v>
       </c>
-      <c r="D41">
+      <c r="E41" s="2">
         <v>-838422000</v>
       </c>
-      <c r="E41">
-        <v>-508449000</v>
-      </c>
-      <c r="H41">
+      <c r="F41" s="2">
+        <v>-508230000</v>
+      </c>
+      <c r="I41" s="2">
         <v>-103416000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
+      <c r="A42" s="2" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Gelir Etkisi</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="2">
+        <v>693000000</v>
+      </c>
+      <c r="C42" s="2">
         <v>1772000000</v>
       </c>
-      <c r="C42">
+      <c r="D42" s="2">
         <v>1226000000</v>
       </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="H42">
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
+      <c r="A43" s="2" t="str">
         <v xml:space="preserve">    SÜRDÜRÜLEN FAALİYETLER DÖNEM NET KARI (ZARARI)</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="2">
+        <v>8023937000</v>
+      </c>
+      <c r="C43" s="2">
         <v>8758937000</v>
       </c>
-      <c r="C43">
+      <c r="D43" s="2">
         <v>7206937000</v>
       </c>
-      <c r="D43">
+      <c r="E43" s="2">
         <v>5655937000</v>
       </c>
-      <c r="E43">
-        <v>4036122000</v>
-      </c>
-      <c r="H43">
+      <c r="F43" s="2">
+        <v>4035873000</v>
+      </c>
+      <c r="I43" s="2">
         <v>668455000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
+      <c r="A44" s="2" t="str">
         <v xml:space="preserve">    DÖNEM NET KARI VEYA ZARARI</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="2">
+        <v>8023937000</v>
+      </c>
+      <c r="C44" s="2">
         <v>8758937000</v>
       </c>
-      <c r="C44">
+      <c r="D44" s="2">
         <v>7206937000</v>
       </c>
-      <c r="D44">
+      <c r="E44" s="2">
         <v>5655937000</v>
       </c>
-      <c r="E44">
-        <v>4036122000</v>
-      </c>
-      <c r="H44">
+      <c r="F44" s="2">
+        <v>4035873000</v>
+      </c>
+      <c r="I44" s="2">
         <v>668455000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
+      <c r="A45" s="2" t="str">
         <v xml:space="preserve">    Grubun Karı (Zararı)</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="2">
+        <v>8023937000</v>
+      </c>
+      <c r="C45" s="2">
         <v>8758937000</v>
       </c>
-      <c r="C45">
+      <c r="D45" s="2">
         <v>7206937000</v>
       </c>
-      <c r="D45">
+      <c r="E45" s="2">
         <v>5655937000</v>
       </c>
-      <c r="E45">
-        <v>4036122000</v>
-      </c>
-      <c r="H45">
+      <c r="F45" s="2">
+        <v>4035873000</v>
+      </c>
+      <c r="I45" s="2">
         <v>668455000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
+      <c r="A46" s="2" t="str">
         <v xml:space="preserve">    Azınlık Payları Karı (Zararı)</v>
       </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="H46">
+      <c r="B46" s="2">
+        <v>0</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J46"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4781,7 +5331,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="2" t="str">
         <v>Kalem</v>
       </c>
     </row>
@@ -4800,7 +5350,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="2" t="str">
         <v>Kalem</v>
       </c>
     </row>
@@ -4819,7 +5369,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="2" t="str">
         <v>Kalem</v>
       </c>
     </row>
